--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/123.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/123.xlsx
@@ -426,13 +426,13 @@
         <v>-18.35164191286164</v>
       </c>
       <c r="E2">
-        <v>-13.75599813016559</v>
+        <v>-18.51474051265198</v>
       </c>
       <c r="F2">
-        <v>-4.128386959725781</v>
+        <v>-5.722964388888328</v>
       </c>
       <c r="G2">
-        <v>-13.43707181310444</v>
+        <v>-15.15519032398478</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.978719767309</v>
       </c>
       <c r="E3">
-        <v>-14.63357110811203</v>
+        <v>-19.16853441903538</v>
       </c>
       <c r="F3">
-        <v>-4.527920983607024</v>
+        <v>-5.742006898743883</v>
       </c>
       <c r="G3">
-        <v>-13.33589160978769</v>
+        <v>-14.95994427971519</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.48523488565776</v>
       </c>
       <c r="E4">
-        <v>-15.44326226068349</v>
+        <v>-19.98095624143347</v>
       </c>
       <c r="F4">
-        <v>-4.526460571875888</v>
+        <v>-5.730913402485592</v>
       </c>
       <c r="G4">
-        <v>-12.88836875324347</v>
+        <v>-14.2825685911066</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.92752102544527</v>
       </c>
       <c r="E5">
-        <v>-15.91496622721847</v>
+        <v>-20.87236370747334</v>
       </c>
       <c r="F5">
-        <v>-4.052540811958055</v>
+        <v>-5.791533329022459</v>
       </c>
       <c r="G5">
-        <v>-11.46750909215259</v>
+        <v>-13.95990792539431</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.31861802795882</v>
       </c>
       <c r="E6">
-        <v>-15.99028380691404</v>
+        <v>-20.95469589340679</v>
       </c>
       <c r="F6">
-        <v>-4.084924178835696</v>
+        <v>-5.498567114776567</v>
       </c>
       <c r="G6">
-        <v>-11.20691287893778</v>
+        <v>-14.25619016424969</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.70111848786267</v>
       </c>
       <c r="E7">
-        <v>-17.86784800065627</v>
+        <v>-21.24031127754457</v>
       </c>
       <c r="F7">
-        <v>-4.483093881604528</v>
+        <v>-5.623855199347783</v>
       </c>
       <c r="G7">
-        <v>-12.22608418647565</v>
+        <v>-13.69783355359621</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.11259737468382</v>
       </c>
       <c r="E8">
-        <v>-17.50326508677274</v>
+        <v>-22.12506188679317</v>
       </c>
       <c r="F8">
-        <v>-4.34497521433135</v>
+        <v>-5.510301767404624</v>
       </c>
       <c r="G8">
-        <v>-11.04095854159966</v>
+        <v>-13.09023257804607</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.58157051811923</v>
       </c>
       <c r="E9">
-        <v>-18.35051540276381</v>
+        <v>-22.21109383599089</v>
       </c>
       <c r="F9">
-        <v>-4.735149514928362</v>
+        <v>-5.926354265665093</v>
       </c>
       <c r="G9">
-        <v>-10.70514673373261</v>
+        <v>-13.69562873026706</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.1255058878013</v>
       </c>
       <c r="E10">
-        <v>-18.50816516839284</v>
+        <v>-23.56212329991327</v>
       </c>
       <c r="F10">
-        <v>-4.837114915273759</v>
+        <v>-5.49549055824257</v>
       </c>
       <c r="G10">
-        <v>-9.917253448113762</v>
+        <v>-12.73904990724019</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.76949587928182</v>
       </c>
       <c r="E11">
-        <v>-18.83211861347956</v>
+        <v>-23.10793094236596</v>
       </c>
       <c r="F11">
-        <v>-4.142861851722299</v>
+        <v>-5.682695792703438</v>
       </c>
       <c r="G11">
-        <v>-10.46798918293584</v>
+        <v>-12.67001179056422</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.52561343763267</v>
       </c>
       <c r="E12">
-        <v>-20.32801396090732</v>
+        <v>-23.51787558038432</v>
       </c>
       <c r="F12">
-        <v>-4.366234435356796</v>
+        <v>-5.57847226281801</v>
       </c>
       <c r="G12">
-        <v>-9.444255943644851</v>
+        <v>-12.94328077210337</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.38620293669948</v>
       </c>
       <c r="E13">
-        <v>-20.3219865620031</v>
+        <v>-23.99334270881967</v>
       </c>
       <c r="F13">
-        <v>-4.088437284990968</v>
+        <v>-5.470791955760699</v>
       </c>
       <c r="G13">
-        <v>-9.078086433182683</v>
+        <v>-12.6167914604749</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.34613522698259</v>
       </c>
       <c r="E14">
-        <v>-20.29079443303827</v>
+        <v>-25.64912941651025</v>
       </c>
       <c r="F14">
-        <v>-4.360565917219439</v>
+        <v>-5.02263442206993</v>
       </c>
       <c r="G14">
-        <v>-9.228947993407271</v>
+        <v>-11.89631412421777</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.39599966300478</v>
       </c>
       <c r="E15">
-        <v>-21.5697622900766</v>
+        <v>-25.23112409475823</v>
       </c>
       <c r="F15">
-        <v>-3.829154146077709</v>
+        <v>-5.163519836468459</v>
       </c>
       <c r="G15">
-        <v>-8.153944335349593</v>
+        <v>-11.9090795878172</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.5110998617398</v>
       </c>
       <c r="E16">
-        <v>-22.85411903118405</v>
+        <v>-26.90589869396298</v>
       </c>
       <c r="F16">
-        <v>-3.751556829620466</v>
+        <v>-4.750932399053901</v>
       </c>
       <c r="G16">
-        <v>-8.31921007921555</v>
+        <v>-11.60234430142157</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.66390312381902</v>
       </c>
       <c r="E17">
-        <v>-23.16070124997734</v>
+        <v>-26.45666501545406</v>
       </c>
       <c r="F17">
-        <v>-3.732849808563044</v>
+        <v>-4.571281046939161</v>
       </c>
       <c r="G17">
-        <v>-8.405122046505175</v>
+        <v>-11.53874541106663</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.8375930357089</v>
       </c>
       <c r="E18">
-        <v>-23.25491615170692</v>
+        <v>-27.27907212303906</v>
       </c>
       <c r="F18">
-        <v>-3.370096954100904</v>
+        <v>-4.169884853136424</v>
       </c>
       <c r="G18">
-        <v>-8.951249501936587</v>
+        <v>-11.62012193096746</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.01258978798351</v>
       </c>
       <c r="E19">
-        <v>-24.22699385371943</v>
+        <v>-28.24712401165875</v>
       </c>
       <c r="F19">
-        <v>-2.85970749090742</v>
+        <v>-4.237607201784895</v>
       </c>
       <c r="G19">
-        <v>-7.954467413880807</v>
+        <v>-11.38365297364285</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.16518816878767</v>
       </c>
       <c r="E20">
-        <v>-25.03774466920868</v>
+        <v>-28.35476583882108</v>
       </c>
       <c r="F20">
-        <v>-2.734353136943979</v>
+        <v>-4.137503142993589</v>
       </c>
       <c r="G20">
-        <v>-7.732011995823941</v>
+        <v>-11.77016578644385</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.28905244884889</v>
       </c>
       <c r="E21">
-        <v>-25.26114787742909</v>
+        <v>-28.58719429573877</v>
       </c>
       <c r="F21">
-        <v>-2.658815141850095</v>
+        <v>-3.547062739095769</v>
       </c>
       <c r="G21">
-        <v>-8.086329753255518</v>
+        <v>-11.73283607494302</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.38904350215488</v>
       </c>
       <c r="E22">
-        <v>-25.84330585348515</v>
+        <v>-29.32451137671964</v>
       </c>
       <c r="F22">
-        <v>-2.619940688004117</v>
+        <v>-3.369141846485477</v>
       </c>
       <c r="G22">
-        <v>-7.844368600881265</v>
+        <v>-12.38741700224096</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.46448929498702</v>
       </c>
       <c r="E23">
-        <v>-26.86077245047654</v>
+        <v>-29.03371994679109</v>
       </c>
       <c r="F23">
-        <v>-2.157830962147996</v>
+        <v>-3.296826200588483</v>
       </c>
       <c r="G23">
-        <v>-7.36675950647615</v>
+        <v>-12.01279566901703</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.51313623443286</v>
       </c>
       <c r="E24">
-        <v>-27.05546513348832</v>
+        <v>-29.30757941240496</v>
       </c>
       <c r="F24">
-        <v>-2.219163284651271</v>
+        <v>-3.240498045565519</v>
       </c>
       <c r="G24">
-        <v>-8.035565847956333</v>
+        <v>-11.59516372814689</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-14.5401082442526</v>
       </c>
       <c r="E25">
-        <v>-25.53309179853771</v>
+        <v>-29.27751940194204</v>
       </c>
       <c r="F25">
-        <v>-1.82760726722639</v>
+        <v>-3.091825977580675</v>
       </c>
       <c r="G25">
-        <v>-9.471514975615211</v>
+        <v>-11.99256492522654</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-14.54441507159142</v>
       </c>
       <c r="E26">
-        <v>-27.26049179418559</v>
+        <v>-30.11768265611112</v>
       </c>
       <c r="F26">
-        <v>-1.756369327320438</v>
+        <v>-2.969473627084979</v>
       </c>
       <c r="G26">
-        <v>-8.274282665702099</v>
+        <v>-12.52665192653163</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-14.51528477600425</v>
       </c>
       <c r="E27">
-        <v>-25.8345975979684</v>
+        <v>-29.94483306747534</v>
       </c>
       <c r="F27">
-        <v>-2.384710024998544</v>
+        <v>-2.619901754736185</v>
       </c>
       <c r="G27">
-        <v>-9.080774596160571</v>
+        <v>-12.82959332773925</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.45113618558146</v>
       </c>
       <c r="E28">
-        <v>-26.09551015639434</v>
+        <v>-29.06889713288268</v>
       </c>
       <c r="F28">
-        <v>-2.172008470246909</v>
+        <v>-2.803733048765451</v>
       </c>
       <c r="G28">
-        <v>-8.693225582605789</v>
+        <v>-12.56106173686681</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.35660591145487</v>
       </c>
       <c r="E29">
-        <v>-25.27346985520396</v>
+        <v>-29.76525416646417</v>
       </c>
       <c r="F29">
-        <v>-2.340878620614214</v>
+        <v>-2.92168925345449</v>
       </c>
       <c r="G29">
-        <v>-8.137371744380001</v>
+        <v>-12.51401226366269</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.23120650811791</v>
       </c>
       <c r="E30">
-        <v>-26.5496708146236</v>
+        <v>-29.08100174390518</v>
       </c>
       <c r="F30">
-        <v>-1.479786563567114</v>
+        <v>-2.800939793883212</v>
       </c>
       <c r="G30">
-        <v>-9.857388853127121</v>
+        <v>-12.51415130657534</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.07682529038244</v>
       </c>
       <c r="E31">
-        <v>-25.68303862987969</v>
+        <v>-29.38422836345879</v>
       </c>
       <c r="F31">
-        <v>-1.925044811348084</v>
+        <v>-2.52310619535166</v>
       </c>
       <c r="G31">
-        <v>-9.032308209465642</v>
+        <v>-12.80681677442907</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.9081323841949</v>
       </c>
       <c r="E32">
-        <v>-25.32753983485554</v>
+        <v>-29.20730994092712</v>
       </c>
       <c r="F32">
-        <v>-1.870854672591746</v>
+        <v>-2.936468984655239</v>
       </c>
       <c r="G32">
-        <v>-8.354983834312913</v>
+        <v>-13.393452065079</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.73930967451777</v>
       </c>
       <c r="E33">
-        <v>-24.86021037421198</v>
+        <v>-29.21779335825488</v>
       </c>
       <c r="F33">
-        <v>-1.794374823760879</v>
+        <v>-2.874760583351093</v>
       </c>
       <c r="G33">
-        <v>-8.924129512878876</v>
+        <v>-12.54008280978445</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.57928286118095</v>
       </c>
       <c r="E34">
-        <v>-25.62339862719867</v>
+        <v>-28.34228989292994</v>
       </c>
       <c r="F34">
-        <v>-2.010841308358238</v>
+        <v>-2.880010775950036</v>
       </c>
       <c r="G34">
-        <v>-7.595720146517685</v>
+        <v>-12.32806223126737</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.44579624589514</v>
       </c>
       <c r="E35">
-        <v>-25.13296942064198</v>
+        <v>-28.99352973997302</v>
       </c>
       <c r="F35">
-        <v>-1.394636193131144</v>
+        <v>-3.052640885958647</v>
       </c>
       <c r="G35">
-        <v>-8.598054019442822</v>
+        <v>-11.80250981636252</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.35474341624527</v>
       </c>
       <c r="E36">
-        <v>-24.59302135081141</v>
+        <v>-28.17849951654652</v>
       </c>
       <c r="F36">
-        <v>-2.096914480080926</v>
+        <v>-2.747113308416703</v>
       </c>
       <c r="G36">
-        <v>-8.107010731239345</v>
+        <v>-12.52294411552764</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.30638733297669</v>
       </c>
       <c r="E37">
-        <v>-22.74910371894617</v>
+        <v>-27.45006730156869</v>
       </c>
       <c r="F37">
-        <v>-2.066783444171497</v>
+        <v>-3.044458272753793</v>
       </c>
       <c r="G37">
-        <v>-9.23890280384386</v>
+        <v>-12.14111572466472</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.29503590319856</v>
       </c>
       <c r="E38">
-        <v>-25.05849413711183</v>
+        <v>-28.03726546919529</v>
       </c>
       <c r="F38">
-        <v>-1.629430306515442</v>
+        <v>-2.7269914358353</v>
       </c>
       <c r="G38">
-        <v>-8.730455977740434</v>
+        <v>-12.10799040599877</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.31867381461789</v>
       </c>
       <c r="E39">
-        <v>-23.28817779329326</v>
+        <v>-27.62589889033852</v>
       </c>
       <c r="F39">
-        <v>-2.351719464814651</v>
+        <v>-2.962009208418353</v>
       </c>
       <c r="G39">
-        <v>-8.645924507940684</v>
+        <v>-11.43301651817893</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.36404270516431</v>
       </c>
       <c r="E40">
-        <v>-21.76393872705149</v>
+        <v>-26.69076447928058</v>
       </c>
       <c r="F40">
-        <v>-2.088225734392962</v>
+        <v>-2.989426512716211</v>
       </c>
       <c r="G40">
-        <v>-8.374161824621911</v>
+        <v>-12.28034733840985</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.40428346673613</v>
       </c>
       <c r="E41">
-        <v>-22.83132269302943</v>
+        <v>-26.53570952925795</v>
       </c>
       <c r="F41">
-        <v>-1.585044724338639</v>
+        <v>-3.173474010637608</v>
       </c>
       <c r="G41">
-        <v>-9.057988111213769</v>
+        <v>-11.44274952206439</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.41834321325417</v>
       </c>
       <c r="E42">
-        <v>-23.31744984927884</v>
+        <v>-25.83295376190362</v>
       </c>
       <c r="F42">
-        <v>-1.929504741444757</v>
+        <v>-3.095887462956601</v>
       </c>
       <c r="G42">
-        <v>-7.618106055454237</v>
+        <v>-11.22415751065185</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.3863864279978</v>
       </c>
       <c r="E43">
-        <v>-21.3347344890785</v>
+        <v>-25.5476100862063</v>
       </c>
       <c r="F43">
-        <v>-1.975704448233691</v>
+        <v>-3.115102273231938</v>
       </c>
       <c r="G43">
-        <v>-7.865463397057501</v>
+        <v>-11.54953116843358</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.28588630516833</v>
       </c>
       <c r="E44">
-        <v>-22.0801530100591</v>
+        <v>-25.39502315451785</v>
       </c>
       <c r="F44">
-        <v>-2.305937255196728</v>
+        <v>-3.141895816875488</v>
       </c>
       <c r="G44">
-        <v>-8.004109044242178</v>
+        <v>-11.91187368825235</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.10446514100969</v>
       </c>
       <c r="E45">
-        <v>-19.34434336543517</v>
+        <v>-24.60023520990563</v>
       </c>
       <c r="F45">
-        <v>-1.945696010699876</v>
+        <v>-3.282833418420393</v>
       </c>
       <c r="G45">
-        <v>-7.294957084274897</v>
+        <v>-11.26230161635533</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.84645947290422</v>
       </c>
       <c r="E46">
-        <v>-20.70720120346558</v>
+        <v>-24.07336990148322</v>
       </c>
       <c r="F46">
-        <v>-1.812809311942779</v>
+        <v>-3.110073254729542</v>
       </c>
       <c r="G46">
-        <v>-8.354848101945803</v>
+        <v>-11.61411660135922</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.52027741464326</v>
       </c>
       <c r="E47">
-        <v>-19.06616826409199</v>
+        <v>-23.04822754104883</v>
       </c>
       <c r="F47">
-        <v>-1.655509797457779</v>
+        <v>-3.247782708505738</v>
       </c>
       <c r="G47">
-        <v>-7.732442366744046</v>
+        <v>-11.15748312349093</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.1351614095933</v>
       </c>
       <c r="E48">
-        <v>-18.2440600357915</v>
+        <v>-23.58858317354009</v>
       </c>
       <c r="F48">
-        <v>-2.323593078019996</v>
+        <v>-3.270809665568759</v>
       </c>
       <c r="G48">
-        <v>-8.022525609077144</v>
+        <v>-11.39804391510207</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.7118134842663</v>
       </c>
       <c r="E49">
-        <v>-19.08540522167658</v>
+        <v>-22.88317372041726</v>
       </c>
       <c r="F49">
-        <v>-2.193758913142216</v>
+        <v>-3.160676562631759</v>
       </c>
       <c r="G49">
-        <v>-7.088432011353004</v>
+        <v>-11.81832098185808</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.26933636045444</v>
       </c>
       <c r="E50">
-        <v>-17.88831670317094</v>
+        <v>-22.40878889726974</v>
       </c>
       <c r="F50">
-        <v>-1.998627859371362</v>
+        <v>-3.748896113522674</v>
       </c>
       <c r="G50">
-        <v>-7.746240720551728</v>
+        <v>-11.88444581845949</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.81781132762475</v>
       </c>
       <c r="E51">
-        <v>-17.64771435066941</v>
+        <v>-21.67386737903893</v>
       </c>
       <c r="F51">
-        <v>-2.731038838965378</v>
+        <v>-3.665440582792832</v>
       </c>
       <c r="G51">
-        <v>-7.3945151202774</v>
+        <v>-11.97591619170955</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.36777064594284</v>
       </c>
       <c r="E52">
-        <v>-18.20780054441208</v>
+        <v>-22.22564382297753</v>
       </c>
       <c r="F52">
-        <v>-2.226499306370464</v>
+        <v>-3.275489941394575</v>
       </c>
       <c r="G52">
-        <v>-6.802837868771157</v>
+        <v>-11.24367317660585</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.932138312720037</v>
       </c>
       <c r="E53">
-        <v>-16.89979158356257</v>
+        <v>-21.25977918730354</v>
       </c>
       <c r="F53">
-        <v>-2.423581165374911</v>
+        <v>-3.812252137590988</v>
       </c>
       <c r="G53">
-        <v>-8.396375585190421</v>
+        <v>-11.19453474916645</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.514957963074513</v>
       </c>
       <c r="E54">
-        <v>-16.66490869373272</v>
+        <v>-21.30268647852622</v>
       </c>
       <c r="F54">
-        <v>-2.586732267193288</v>
+        <v>-3.624636032898331</v>
       </c>
       <c r="G54">
-        <v>-8.319868877777864</v>
+        <v>-11.72502649801588</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.11163705104064</v>
       </c>
       <c r="E55">
-        <v>-16.3943776565145</v>
+        <v>-21.46231971577061</v>
       </c>
       <c r="F55">
-        <v>-2.793286507448747</v>
+        <v>-3.939129859208177</v>
       </c>
       <c r="G55">
-        <v>-8.837975875764883</v>
+        <v>-12.19857024249877</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.723108676177553</v>
       </c>
       <c r="E56">
-        <v>-16.30875326997747</v>
+        <v>-20.91031231965762</v>
       </c>
       <c r="F56">
-        <v>-2.043409401166703</v>
+        <v>-3.779831494180221</v>
       </c>
       <c r="G56">
-        <v>-7.998812171379345</v>
+        <v>-11.89452974017211</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.347004838818506</v>
       </c>
       <c r="E57">
-        <v>-15.80982411770838</v>
+        <v>-20.10312088473839</v>
       </c>
       <c r="F57">
-        <v>-2.714136830478657</v>
+        <v>-3.637206508235813</v>
       </c>
       <c r="G57">
-        <v>-8.960419713080368</v>
+        <v>-11.92348046091303</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.975321464617606</v>
       </c>
       <c r="E58">
-        <v>-14.03836659843987</v>
+        <v>-20.77640987172481</v>
       </c>
       <c r="F58">
-        <v>-2.747684053557232</v>
+        <v>-3.302908902427239</v>
       </c>
       <c r="G58">
-        <v>-9.176800280072671</v>
+        <v>-11.78893657965151</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.605332980637206</v>
       </c>
       <c r="E59">
-        <v>-15.04731060734883</v>
+        <v>-18.96514253745487</v>
       </c>
       <c r="F59">
-        <v>-2.578784910330829</v>
+        <v>-3.73856223017275</v>
       </c>
       <c r="G59">
-        <v>-10.17055652950556</v>
+        <v>-12.27677525977298</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.23990444969372</v>
       </c>
       <c r="E60">
-        <v>-16.64125647399066</v>
+        <v>-19.34978659119239</v>
       </c>
       <c r="F60">
-        <v>-1.967924421586598</v>
+        <v>-3.408008845024829</v>
       </c>
       <c r="G60">
-        <v>-8.190409994464664</v>
+        <v>-12.63611511478763</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.880000196023794</v>
       </c>
       <c r="E61">
-        <v>-14.35459899534351</v>
+        <v>-19.74751340633806</v>
       </c>
       <c r="F61">
-        <v>-2.6700014152575</v>
+        <v>-3.589061794785106</v>
       </c>
       <c r="G61">
-        <v>-9.389486278243149</v>
+        <v>-12.30894383077807</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.525184326173157</v>
       </c>
       <c r="E62">
-        <v>-13.84937526420376</v>
+        <v>-18.79092761390579</v>
       </c>
       <c r="F62">
-        <v>-2.620496522531395</v>
+        <v>-3.665514307491681</v>
       </c>
       <c r="G62">
-        <v>-9.611004811912402</v>
+        <v>-12.14895178595618</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.182419413465221</v>
       </c>
       <c r="E63">
-        <v>-15.03061412368255</v>
+        <v>-19.34508603517243</v>
       </c>
       <c r="F63">
-        <v>-1.962342053659132</v>
+        <v>-3.888110710869756</v>
       </c>
       <c r="G63">
-        <v>-8.771394183879062</v>
+        <v>-12.52527805013283</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.857134342946305</v>
       </c>
       <c r="E64">
-        <v>-14.49913882872033</v>
+        <v>-19.31297009751003</v>
       </c>
       <c r="F64">
-        <v>-2.350286389207808</v>
+        <v>-3.547304622377386</v>
       </c>
       <c r="G64">
-        <v>-9.592290297978902</v>
+        <v>-12.38224261956308</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.550509032433692</v>
       </c>
       <c r="E65">
-        <v>-14.21020407313493</v>
+        <v>-17.92002054969864</v>
       </c>
       <c r="F65">
-        <v>-2.865584757630282</v>
+        <v>-3.791179299231171</v>
       </c>
       <c r="G65">
-        <v>-10.39913314626454</v>
+        <v>-12.96541507957893</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.266977060242461</v>
       </c>
       <c r="E66">
-        <v>-13.79700799077906</v>
+        <v>-19.28833972738231</v>
       </c>
       <c r="F66">
-        <v>-2.426521041287447</v>
+        <v>-3.668711805666487</v>
       </c>
       <c r="G66">
-        <v>-8.18084582840171</v>
+        <v>-12.57276782589367</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.013260160178618</v>
       </c>
       <c r="E67">
-        <v>-14.40909918002582</v>
+        <v>-18.71385751476924</v>
       </c>
       <c r="F67">
-        <v>-2.002813599857708</v>
+        <v>-3.791234799847159</v>
       </c>
       <c r="G67">
-        <v>-9.750471474390819</v>
+        <v>-12.6594974979315</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.792771438480952</v>
       </c>
       <c r="E68">
-        <v>-14.45389031643569</v>
+        <v>-17.84585773087503</v>
       </c>
       <c r="F68">
-        <v>-2.078802226818715</v>
+        <v>-3.741261051171071</v>
       </c>
       <c r="G68">
-        <v>-10.07411371685551</v>
+        <v>-12.77645907183395</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.605776590492406</v>
       </c>
       <c r="E69">
-        <v>-12.64101084541902</v>
+        <v>-19.19887972336078</v>
       </c>
       <c r="F69">
-        <v>-1.915109372718907</v>
+        <v>-3.84287522373768</v>
       </c>
       <c r="G69">
-        <v>-9.8018842466157</v>
+        <v>-12.95742342264713</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.454196946621066</v>
       </c>
       <c r="E70">
-        <v>-15.11333122990665</v>
+        <v>-18.14273090139587</v>
       </c>
       <c r="F70">
-        <v>-2.12350507371079</v>
+        <v>-3.877714699964622</v>
       </c>
       <c r="G70">
-        <v>-9.376979037195783</v>
+        <v>-12.61439793605001</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.335296015615765</v>
       </c>
       <c r="E71">
-        <v>-13.51177752693193</v>
+        <v>-18.95699581271507</v>
       </c>
       <c r="F71">
-        <v>-2.404151807942248</v>
+        <v>-4.074770879579583</v>
       </c>
       <c r="G71">
-        <v>-9.119269619691217</v>
+        <v>-12.67926145480095</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.240411893453124</v>
       </c>
       <c r="E72">
-        <v>-14.24528163279835</v>
+        <v>-19.13549920114943</v>
       </c>
       <c r="F72">
-        <v>-2.487333977429167</v>
+        <v>-4.149755525248397</v>
       </c>
       <c r="G72">
-        <v>-10.27127987753788</v>
+        <v>-12.13641474999896</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.161789682830976</v>
       </c>
       <c r="E73">
-        <v>-14.95375686282437</v>
+        <v>-19.22372746024087</v>
       </c>
       <c r="F73">
-        <v>-3.060786222630375</v>
+        <v>-4.165486222227559</v>
       </c>
       <c r="G73">
-        <v>-8.786371091898724</v>
+        <v>-12.64567597030504</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.0927805124436</v>
       </c>
       <c r="E74">
-        <v>-14.40887728479944</v>
+        <v>-18.476379809333</v>
       </c>
       <c r="F74">
-        <v>-3.017194216425453</v>
+        <v>-4.109616154378344</v>
       </c>
       <c r="G74">
-        <v>-9.149355857552113</v>
+        <v>-12.87334549758626</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.024936671137001</v>
       </c>
       <c r="E75">
-        <v>-13.96676689590459</v>
+        <v>-19.33409995722982</v>
       </c>
       <c r="F75">
-        <v>-3.086127638216817</v>
+        <v>-4.171003149130204</v>
       </c>
       <c r="G75">
-        <v>-8.747472181812288</v>
+        <v>-12.63798557301732</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.950532015537249</v>
       </c>
       <c r="E76">
-        <v>-16.49169003446532</v>
+        <v>-19.08467160888733</v>
       </c>
       <c r="F76">
-        <v>-3.000458709786695</v>
+        <v>-4.054336712487324</v>
       </c>
       <c r="G76">
-        <v>-8.499677848197839</v>
+        <v>-12.69377819699065</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.866992011672435</v>
       </c>
       <c r="E77">
-        <v>-15.56069012017639</v>
+        <v>-19.25088471886487</v>
       </c>
       <c r="F77">
-        <v>-2.647645435790746</v>
+        <v>-4.293719981283131</v>
       </c>
       <c r="G77">
-        <v>-9.17145374902675</v>
+        <v>-11.915174302155</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.772734127993497</v>
       </c>
       <c r="E78">
-        <v>-15.58307889567032</v>
+        <v>-20.51642112199644</v>
       </c>
       <c r="F78">
-        <v>-2.997662969802247</v>
+        <v>-4.471889384114262</v>
       </c>
       <c r="G78">
-        <v>-9.572526341109453</v>
+        <v>-11.96487883288162</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.666095439067609</v>
       </c>
       <c r="E79">
-        <v>-16.50244968870755</v>
+        <v>-20.45769134259096</v>
       </c>
       <c r="F79">
-        <v>-3.290871067329757</v>
+        <v>-4.5172615518678</v>
       </c>
       <c r="G79">
-        <v>-9.128161745009699</v>
+        <v>-12.53207128957941</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.550877270419459</v>
       </c>
       <c r="E80">
-        <v>-17.75927330784837</v>
+        <v>-21.6176418457597</v>
       </c>
       <c r="F80">
-        <v>-3.240361364944057</v>
+        <v>-4.384350002088619</v>
       </c>
       <c r="G80">
-        <v>-8.939318295813052</v>
+        <v>-12.49203355182747</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.437054387357028</v>
       </c>
       <c r="E81">
-        <v>-16.50937825393929</v>
+        <v>-21.67187485047555</v>
       </c>
       <c r="F81">
-        <v>-3.003072208942527</v>
+        <v>-4.644570024534445</v>
       </c>
       <c r="G81">
-        <v>-9.774330576092346</v>
+        <v>-12.70004174915095</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.334590247312374</v>
       </c>
       <c r="E82">
-        <v>-18.85150501070639</v>
+        <v>-21.4278353862022</v>
       </c>
       <c r="F82">
-        <v>-3.358749977417357</v>
+        <v>-4.535744913726465</v>
       </c>
       <c r="G82">
-        <v>-8.793829750998702</v>
+        <v>-11.45048626698966</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.25275986359165</v>
       </c>
       <c r="E83">
-        <v>-18.58222836078829</v>
+        <v>-23.03888529917101</v>
       </c>
       <c r="F83">
-        <v>-3.519073032922576</v>
+        <v>-4.942703594639001</v>
       </c>
       <c r="G83">
-        <v>-8.722967523730603</v>
+        <v>-12.21365308797569</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.202401641991736</v>
       </c>
       <c r="E84">
-        <v>-20.01088945462417</v>
+        <v>-23.84763452914887</v>
       </c>
       <c r="F84">
-        <v>-3.89578470648929</v>
+        <v>-5.033920927933074</v>
       </c>
       <c r="G84">
-        <v>-8.991283929142993</v>
+        <v>-11.53543486552736</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.192120585747499</v>
       </c>
       <c r="E85">
-        <v>-20.21803996963104</v>
+        <v>-24.38022382871698</v>
       </c>
       <c r="F85">
-        <v>-3.810606999929028</v>
+        <v>-5.019718568812077</v>
       </c>
       <c r="G85">
-        <v>-8.091441235568153</v>
+        <v>-11.3457306744905</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.225907275041523</v>
       </c>
       <c r="E86">
-        <v>-21.47823730190757</v>
+        <v>-25.46289592294481</v>
       </c>
       <c r="F86">
-        <v>-3.939469489843325</v>
+        <v>-4.770529086701929</v>
       </c>
       <c r="G86">
-        <v>-7.955185802262829</v>
+        <v>-11.21720867556492</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.305931409853673</v>
       </c>
       <c r="E87">
-        <v>-24.29936339683601</v>
+        <v>-25.97992991429657</v>
       </c>
       <c r="F87">
-        <v>-4.032830637975843</v>
+        <v>-4.899580444384064</v>
       </c>
       <c r="G87">
-        <v>-8.295238418965686</v>
+        <v>-11.17665449270885</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.435347861710024</v>
       </c>
       <c r="E88">
-        <v>-22.70495109737139</v>
+        <v>-27.40067976404104</v>
       </c>
       <c r="F88">
-        <v>-3.845981601498178</v>
+        <v>-5.429743037482373</v>
       </c>
       <c r="G88">
-        <v>-8.473392116616026</v>
+        <v>-11.61947306404176</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.611462986815439</v>
       </c>
       <c r="E89">
-        <v>-24.91001905982234</v>
+        <v>-28.26589906489455</v>
       </c>
       <c r="F89">
-        <v>-4.515868237896291</v>
+        <v>-5.339672164673774</v>
       </c>
       <c r="G89">
-        <v>-8.400738884211181</v>
+        <v>-11.28495236893502</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.828176438763222</v>
       </c>
       <c r="E90">
-        <v>-26.42845715086028</v>
+        <v>-30.06012575147363</v>
       </c>
       <c r="F90">
-        <v>-4.007022851541625</v>
+        <v>-5.271410548846081</v>
       </c>
       <c r="G90">
-        <v>-8.156652361600717</v>
+        <v>-11.17263880096971</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.082011025484304</v>
       </c>
       <c r="E91">
-        <v>-28.63549047103057</v>
+        <v>-31.58567354670361</v>
       </c>
       <c r="F91">
-        <v>-4.31941262464836</v>
+        <v>-5.57656370432196</v>
       </c>
       <c r="G91">
-        <v>-8.477808384365414</v>
+        <v>-11.29984320277067</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.369545448094282</v>
       </c>
       <c r="E92">
-        <v>-29.70091134352619</v>
+        <v>-32.70165709573187</v>
       </c>
       <c r="F92">
-        <v>-4.154782058648584</v>
+        <v>-5.369937396102457</v>
       </c>
       <c r="G92">
-        <v>-9.3769889688324</v>
+        <v>-11.36494177025489</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.683533982863503</v>
       </c>
       <c r="E93">
-        <v>-30.43431808720144</v>
+        <v>-34.18686977297553</v>
       </c>
       <c r="F93">
-        <v>-4.599676653139725</v>
+        <v>-5.76487895110258</v>
       </c>
       <c r="G93">
-        <v>-8.595852506659206</v>
+        <v>-11.70796394630648</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.01443606304886</v>
       </c>
       <c r="E94">
-        <v>-33.12328066821602</v>
+        <v>-36.43833874434608</v>
       </c>
       <c r="F94">
-        <v>-4.556230439597697</v>
+        <v>-5.600232646122151</v>
       </c>
       <c r="G94">
-        <v>-9.068710968215468</v>
+        <v>-11.82665031443489</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.353621281212068</v>
       </c>
       <c r="E95">
-        <v>-34.43407690481725</v>
+        <v>-38.96522950486315</v>
       </c>
       <c r="F95">
-        <v>-4.964622196117076</v>
+        <v>-6.038652720993011</v>
       </c>
       <c r="G95">
-        <v>-7.845941110012419</v>
+        <v>-11.54020205110391</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.686639119780087</v>
       </c>
       <c r="E96">
-        <v>-36.99445573062103</v>
+        <v>-39.30667191656748</v>
       </c>
       <c r="F96">
-        <v>-4.731818649601705</v>
+        <v>-6.00183096157117</v>
       </c>
       <c r="G96">
-        <v>-8.738563503766109</v>
+        <v>-12.31389640690482</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.994847539542288</v>
       </c>
       <c r="E97">
-        <v>-38.51023107894247</v>
+        <v>-42.17370541674868</v>
       </c>
       <c r="F97">
-        <v>-4.863572970119175</v>
+        <v>-6.087697869810562</v>
       </c>
       <c r="G97">
-        <v>-9.490199694638857</v>
+        <v>-12.83333093365309</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.266056987481487</v>
       </c>
       <c r="E98">
-        <v>-41.60450114059156</v>
+        <v>-44.2286703155044</v>
       </c>
       <c r="F98">
-        <v>-4.668204174903718</v>
+        <v>-6.409410918035805</v>
       </c>
       <c r="G98">
-        <v>-10.11312187494474</v>
+        <v>-13.31356198012531</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.48503973725952</v>
       </c>
       <c r="E99">
-        <v>-45.22494365413989</v>
+        <v>-45.40611884223876</v>
       </c>
       <c r="F99">
-        <v>-5.335552693579652</v>
+        <v>-6.467273209488754</v>
       </c>
       <c r="G99">
-        <v>-9.272501530521923</v>
+        <v>-13.09187460863355</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.645181525205952</v>
       </c>
       <c r="E100">
-        <v>-44.93182685280841</v>
+        <v>-47.8688162194601</v>
       </c>
       <c r="F100">
-        <v>-5.76136087474289</v>
+        <v>-6.995054660487715</v>
       </c>
       <c r="G100">
-        <v>-9.775029101201133</v>
+        <v>-13.5361796149136</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.734209146071652</v>
       </c>
       <c r="E101">
-        <v>-47.58858971939145</v>
+        <v>-49.6448169302768</v>
       </c>
       <c r="F101">
-        <v>-5.743486362925283</v>
+        <v>-6.653101283142468</v>
       </c>
       <c r="G101">
-        <v>-10.4184766638505</v>
+        <v>-13.61131741174567</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.768161802936432</v>
       </c>
       <c r="E102">
-        <v>-50.24685264298953</v>
+        <v>-51.83798293091709</v>
       </c>
       <c r="F102">
-        <v>-5.718040573046087</v>
+        <v>-6.745615011421923</v>
       </c>
       <c r="G102">
-        <v>-10.61727492348373</v>
+        <v>-14.20292679706836</v>
       </c>
     </row>
   </sheetData>
